--- a/data/trans_dic/IP38E_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente</t>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,41; 100,0</t>
+          <t>77,74; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,32; 100,0</t>
+          <t>84,09; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,34; 98,3</t>
+          <t>84,71; 98,52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,41; 89,95</t>
+          <t>64,66; 90,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,33; 94,36</t>
+          <t>73,17; 93,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,95; 90,37</t>
+          <t>73,43; 89,91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,61; 91,92</t>
+          <t>59,12; 91,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,64; 94,58</t>
+          <t>70,65; 94,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,36; 91,43</t>
+          <t>72,82; 90,85</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,44; 97,43</t>
+          <t>64,07; 97,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90,01; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,88; 98,84</t>
+          <t>82,33; 98,76</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,17; 100,0</t>
+          <t>55,33; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,38; 100,0</t>
+          <t>75,5; 100,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67,49; 93,81</t>
+          <t>66,38; 92,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,77; 92,7</t>
+          <t>57,84; 92,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,69; 90,18</t>
+          <t>69,85; 90,41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,99; 91,77</t>
+          <t>59,62; 91,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,89; 96,69</t>
+          <t>77,1; 96,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,74; 91,91</t>
+          <t>73,69; 92,46</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,18; 98,19</t>
+          <t>83,08; 97,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83,11; 96,47</t>
+          <t>82,66; 96,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,76; 96,05</t>
+          <t>86,66; 96,19</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,27; 90,39</t>
+          <t>80,42; 90,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85,12; 92,46</t>
+          <t>85,06; 92,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85,02; 91,0</t>
+          <t>85,05; 90,96</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>18040</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25788</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43828</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>15025; 19328</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22904; 27237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39445; 45875</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>21818</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31987</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53805</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>17787; 24763</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>27188; 34921</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47481; 58139</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>14974</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18356</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33330</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11074; 17135</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15000; 20161</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>29098; 36307</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15398</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19995</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35393</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>11230; 17018</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30889; 37056</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5921</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12237</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3858; 6972</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9735; 12893</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>16568</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21139</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37707</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>13267; 18481</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14963; 24026</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>32034; 41462</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>28952</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>41776</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>70727</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>21667; 33397</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>36033; 44985</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>61213; 76810</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>46577</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>48278</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>94855</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>41690; 49111</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>43618; 51120</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>89210; 99021</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>168247</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>213635</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>381882</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>157227; 176039</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>202410; 220819</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>368685; 394305</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38E_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,74; 100,0</t>
+          <t>78,52; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84,09; 100,0</t>
+          <t>80,57; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,71; 98,52</t>
+          <t>85,7; 98,41</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,66; 90,02</t>
+          <t>62,23; 89,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,17; 93,99</t>
+          <t>71,77; 94,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,43; 89,91</t>
+          <t>73,68; 90,14</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,12; 91,48</t>
+          <t>61,38; 91,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,65; 94,95</t>
+          <t>72,49; 94,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,82; 90,85</t>
+          <t>72,68; 90,78</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,07; 97,1</t>
+          <t>62,3; 97,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,33; 98,76</t>
+          <t>84,27; 98,79</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,33; 100,0</t>
+          <t>55,18; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,5; 100,0</t>
+          <t>75,78; 100,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66,38; 92,46</t>
+          <t>68,38; 93,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,84; 92,87</t>
+          <t>59,83; 93,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,85; 90,41</t>
+          <t>67,51; 90,08</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,62; 91,91</t>
+          <t>53,55; 91,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,1; 96,26</t>
+          <t>77,11; 95,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,69; 92,46</t>
+          <t>73,52; 91,96</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,08; 97,87</t>
+          <t>83,03; 98,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,66; 96,88</t>
+          <t>81,89; 96,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,66; 96,19</t>
+          <t>85,85; 96,18</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,42; 90,04</t>
+          <t>80,54; 90,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85,06; 92,8</t>
+          <t>85,13; 92,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85,05; 90,96</t>
+          <t>85,07; 90,66</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15025; 19328</t>
+          <t>15177; 19328</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22904; 27237</t>
+          <t>21946; 27237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39445; 45875</t>
+          <t>39907; 45825</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17787; 24763</t>
+          <t>17119; 24702</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27188; 34921</t>
+          <t>26665; 34924</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47481; 58139</t>
+          <t>47645; 58290</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11074; 17135</t>
+          <t>11497; 17158</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15000; 20161</t>
+          <t>15390; 20168</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29098; 36307</t>
+          <t>29043; 36279</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11230; 17018</t>
+          <t>10918; 17008</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30889; 37056</t>
+          <t>31619; 37069</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3858; 6972</t>
+          <t>3847; 6972</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9735; 12893</t>
+          <t>9771; 12893</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13267; 18481</t>
+          <t>13668; 18719</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14963; 24026</t>
+          <t>15477; 24060</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32034; 41462</t>
+          <t>30958; 41310</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21667; 33397</t>
+          <t>19458; 33264</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36033; 44985</t>
+          <t>36039; 44854</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61213; 76810</t>
+          <t>61075; 76393</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41690; 49111</t>
+          <t>41665; 49271</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43618; 51120</t>
+          <t>43210; 50967</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89210; 99021</t>
+          <t>88382; 99013</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>157227; 176039</t>
+          <t>157476; 176004</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202410; 220819</t>
+          <t>202587; 220907</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>368685; 394305</t>
+          <t>368776; 392975</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,52; 100,0</t>
+          <t>82,41; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,57; 100,0</t>
+          <t>75,54; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,7; 98,41</t>
+          <t>84,45; 98,08</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,23; 89,8</t>
+          <t>72,22; 94,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,77; 94,0</t>
+          <t>62,81; 89,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,68; 90,14</t>
+          <t>71,71; 89,97</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,38; 91,61</t>
+          <t>71,77; 94,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,49; 94,99</t>
+          <t>61,19; 91,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72,68; 90,78</t>
+          <t>71,71; 91,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,3; 97,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>59,76; 97,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,27; 98,79</t>
+          <t>80,79; 99,02</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>60,91; 100,0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>55,18; 100,0</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,78; 100,0</t>
+          <t>75,71; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,38; 93,65</t>
+          <t>61,0; 92,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,83; 93,0</t>
+          <t>66,55; 93,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67,51; 90,08</t>
+          <t>67,81; 89,85</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,55; 91,54</t>
+          <t>77,42; 96,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>77,11; 95,98</t>
+          <t>71,83; 93,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,52; 91,96</t>
+          <t>77,76; 92,73</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,03; 98,19</t>
+          <t>81,98; 96,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,89; 96,59</t>
+          <t>82,32; 97,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,85; 96,18</t>
+          <t>86,15; 95,99</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,54; 90,02</t>
+          <t>84,72; 92,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85,13; 92,83</t>
+          <t>82,0; 90,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85,07; 90,66</t>
+          <t>85,25; 91,16</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>33033</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15177; 19328</t>
+          <t>17549; 21295</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21946; 27237</t>
+          <t>10631; 14073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39907; 45825</t>
+          <t>29869; 34688</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>50851</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17119; 24702</t>
+          <t>24503; 31983</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26665; 34924</t>
+          <t>17320; 24793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47645; 58290</t>
+          <t>44102; 55333</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33330</t>
+          <t>30265</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11497; 17158</t>
+          <t>13216; 17431</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15390; 20168</t>
+          <t>11144; 16687</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29043; 36279</t>
+          <t>26265; 33444</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>15424</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>34409</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10918; 17008</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10502; 17201</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31619; 37069</t>
+          <t>29537; 36201</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12498</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4196; 6889</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3847; 6972</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9771; 12893</t>
+          <t>9955; 13149</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16568</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37707</t>
+          <t>35064</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13668; 18719</t>
+          <t>14075; 21316</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15477; 24060</t>
+          <t>13181; 18547</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30958; 41310</t>
+          <t>29078; 38531</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>28952</t>
+          <t>39787</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>29785</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70727</t>
+          <t>69572</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19458; 33264</t>
+          <t>34648; 43172</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36039; 44854</t>
+          <t>24997; 32634</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61075; 76393</t>
+          <t>61865; 73777</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>46577</t>
+          <t>48770</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>48278</t>
+          <t>50221</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94855</t>
+          <t>98991</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41665; 49271</t>
+          <t>43813; 51448</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43210; 50967</t>
+          <t>44652; 53139</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>88382; 99013</t>
+          <t>92774; 103363</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>247</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>168247</t>
+          <t>197686</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>381882</t>
+          <t>364684</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>157476; 176004</t>
+          <t>187060; 203898</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202587; 220907</t>
+          <t>157881; 174815</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>368776; 392975</t>
+          <t>352379; 376801</t>
         </is>
       </c>
     </row>
